--- a/osmosis.xlsx
+++ b/osmosis.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="269">
   <si>
     <t>delegator_address</t>
   </si>
@@ -19,126 +19,405 @@
     <t>amount</t>
   </si>
   <si>
+    <t>osmo1qfl9rqp6gg2k0ey648wlq36fd6d0xh3xmvsv3x</t>
+  </si>
+  <si>
+    <t>5081000000</t>
+  </si>
+  <si>
     <t>osmo1qvcy2gqxrdgnnypgsjcr2xz57lf4cs6nzts2lq</t>
   </si>
   <si>
+    <t>26965100000</t>
+  </si>
+  <si>
     <t>osmo1qe6q4wwjzse3rkv07czlevhngxn56sus4q96ya</t>
   </si>
   <si>
+    <t>10176473167</t>
+  </si>
+  <si>
     <t>osmo1qm0q9ec5ylrgz2sz78j53xnrfcsse74av2j62z</t>
   </si>
   <si>
+    <t>2914012225</t>
+  </si>
+  <si>
     <t>osmo1przkvlx2f8cxxg4mpj95layg9u8mlmywmv88l7</t>
   </si>
   <si>
+    <t>677783402</t>
+  </si>
+  <si>
     <t>osmo1pvp8emynjnkeamettmydn9s2q3fevgrvc9m5z0</t>
   </si>
   <si>
+    <t>1012050000</t>
+  </si>
+  <si>
+    <t>osmo1pv8dv88w6cpjjanep0389lzen4r8xdgratlcpr</t>
+  </si>
+  <si>
+    <t>2002000000</t>
+  </si>
+  <si>
     <t>osmo1pme8tquascj9t2kay0qxh42f688x5cmre20qzn</t>
   </si>
   <si>
+    <t>10039600517</t>
+  </si>
+  <si>
     <t>osmo1pa56a9fg5jhxrduru275vn2y7fpkxmx69s8jm3</t>
   </si>
   <si>
+    <t>4884519682</t>
+  </si>
+  <si>
     <t>osmo1pls6ps584ymly39fmudhge0q9m4jmdx2r5jrgn</t>
   </si>
   <si>
+    <t>1006609159</t>
+  </si>
+  <si>
+    <t>osmo1ztgk3hcdl4vwxdqnmkkyzgxt0ud6yw7l73vysg</t>
+  </si>
+  <si>
+    <t>2003000000</t>
+  </si>
+  <si>
     <t>osmo1za2uuu8w5h79rq78tvd9hj4gqyg9lsqm5fvqxg</t>
   </si>
   <si>
+    <t>1466999086</t>
+  </si>
+  <si>
     <t>osmo1ry3e3fvjn6e6276ym5kt8f0xr0padqtjmdghyj</t>
   </si>
   <si>
+    <t>1600618122</t>
+  </si>
+  <si>
     <t>osmo1rxwnxskx7w9jjecfzjve35juw3qxughsrgppu5</t>
   </si>
   <si>
+    <t>5193000055</t>
+  </si>
+  <si>
     <t>osmo1r0vf3l0yn57unvhz7wecyyu9vvtgyh3xrmztew</t>
   </si>
   <si>
+    <t>599583964</t>
+  </si>
+  <si>
+    <t>osmo1rkp99zqnf4tlme3a5rfwh6ljgyymcjlyqjepkk</t>
+  </si>
+  <si>
+    <t>5085000000</t>
+  </si>
+  <si>
     <t>osmo1rhgsg2qedccgwrpws524tagm4v7rlpdrl55zkg</t>
   </si>
   <si>
+    <t>11000000000</t>
+  </si>
+  <si>
+    <t>osmo1rcv6x4e0pddxulx7525uf468ttk9pedmh74ffm</t>
+  </si>
+  <si>
+    <t>3282339578</t>
+  </si>
+  <si>
     <t>osmo1rc6zk2k0las34k4zn5msp4d48yuukg0jgvtccd</t>
   </si>
   <si>
+    <t>614000000</t>
+  </si>
+  <si>
     <t>osmo1r7sp8qf07jtj437tcz47jpthlqw3ffthlvdjjy</t>
   </si>
   <si>
+    <t>569000000</t>
+  </si>
+  <si>
     <t>osmo1yp542l3cwq8j0m9zkhcv8exrz2cp7l9q9lptg0</t>
   </si>
   <si>
+    <t>59333871849</t>
+  </si>
+  <si>
     <t>osmo1yyvdwarlwt4sz6qslzs5sx5jlzu6guaj8kntne</t>
   </si>
   <si>
+    <t>1100000000</t>
+  </si>
+  <si>
     <t>osmo1ysthp74n2wxt4flmzyxrhza8rvxzr9mcejk80x</t>
   </si>
   <si>
+    <t>1009917388</t>
+  </si>
+  <si>
     <t>osmo1yn32acr8a3gnfshkftvmj35symffwywuvu2qdc</t>
   </si>
   <si>
+    <t>1088500000</t>
+  </si>
+  <si>
+    <t>osmo1ymwgg85shgthy4gsp7qf59jpf0pz4c3rmqlqvy</t>
+  </si>
+  <si>
+    <t>578914369</t>
+  </si>
+  <si>
+    <t>osmo19qr4snrf00laf3k3w6f5p2za38lq5mymqjh30r</t>
+  </si>
+  <si>
+    <t>2001000000</t>
+  </si>
+  <si>
+    <t>osmo198tu6srltcq85n05mtvfd0pxztfajs2ug2yst5</t>
+  </si>
+  <si>
+    <t>2001200000</t>
+  </si>
+  <si>
     <t>osmo19g9flltdr2ahajrkefdqxc34h5uc532dna8p56</t>
   </si>
   <si>
+    <t>5000000000</t>
+  </si>
+  <si>
+    <t>osmo192lxclzf8lqd4u8dhpn8gcjpkvlwcj6ajedl5d</t>
+  </si>
+  <si>
+    <t>5084000000</t>
+  </si>
+  <si>
     <t>osmo190afz896pj6c4wpk6tt93qt757vkjyvwj9dnax</t>
   </si>
   <si>
+    <t>1000000000</t>
+  </si>
+  <si>
+    <t>osmo194r7queh98l3x0gglua73kpx7d3dwyucneqtt8</t>
+  </si>
+  <si>
+    <t>osmo19uch0afju3c4uvxvlsd08xwjs5v3xxxvskkqkk</t>
+  </si>
+  <si>
     <t>osmo1xpcl957yz4rvh2vwgn426lp6hqunqgq5gl88n4</t>
   </si>
   <si>
+    <t>1030400000</t>
+  </si>
+  <si>
+    <t>osmo1xfldjl4afha988uaaqry96r364mhff2y3fk34w</t>
+  </si>
+  <si>
+    <t>5082000000</t>
+  </si>
+  <si>
+    <t>osmo1xvecfph28wxp8sqyvss5udmtfr37ppf0pvjmy5</t>
+  </si>
+  <si>
+    <t>osmo1x3xqdgpcc075wpr2h6zpcywewjl8pjl6vzhha4</t>
+  </si>
+  <si>
+    <t>2599287481</t>
+  </si>
+  <si>
+    <t>osmo1x3sfh304h4vfxtnachyh0wfqd9yxn2uwql53yj</t>
+  </si>
+  <si>
+    <t>osmo1xj5geh7cekcqlhqz8d5dvdssdzl3sf8kfw2ntj</t>
+  </si>
+  <si>
+    <t>osmo1xarnf65hj3g5ypzrp3z7edw5emxjkmk62sfvts</t>
+  </si>
+  <si>
     <t>osmo18xfkdv9j6shecq0pjdwwpyk5f4encktmzvc82h</t>
   </si>
   <si>
+    <t>589905867</t>
+  </si>
+  <si>
     <t>osmo18gd7nsv2qrx9rv8n0gh37l0x8qmwnrhat7vz0k</t>
   </si>
   <si>
+    <t>6000000000</t>
+  </si>
+  <si>
     <t>osmo18gn8ga2fvd2v9mvdpxm98zmd7lctmegnpcz0q8</t>
   </si>
   <si>
+    <t>502900000</t>
+  </si>
+  <si>
+    <t>osmo183fk2u38mt2yxqvt8axcgaumlrufjmmg8v22wa</t>
+  </si>
+  <si>
+    <t>5090000000</t>
+  </si>
+  <si>
     <t>osmo18nf84jgwkqypaplz45xyf3yegpu4vvhz4j2lnl</t>
   </si>
   <si>
-    <t>osmo1gdplq3dvf80ld3yum3lytfamj73kfgu3cf3dgh</t>
+    <t>2750489740</t>
+  </si>
+  <si>
+    <t>osmo18kvjxrrp935gss49xpuqkn285m64zs9v56q7n3</t>
+  </si>
+  <si>
+    <t>1092000000</t>
+  </si>
+  <si>
+    <t>osmo18crvw4qkw8ju6s9jqyw6w3wx5ghh3unvtpdlw7</t>
+  </si>
+  <si>
+    <t>2682436092</t>
+  </si>
+  <si>
+    <t>osmo1fqydaajtycl55hvazm7um3jj9evm5qawn6shps</t>
   </si>
   <si>
     <t>osmo1frdg5m52d9vmnrm5e9n99zyp9qzq3l8u2hr4qs</t>
   </si>
   <si>
+    <t>3000000000</t>
+  </si>
+  <si>
     <t>osmo1ffe8yjw4tqf6lqwmv58adm52q2dzyt2ppkgud5</t>
   </si>
   <si>
+    <t>5147000000</t>
+  </si>
+  <si>
+    <t>osmo1fsacnsrdljx3ulcd82amand8knt3kn25gcg8pr</t>
+  </si>
+  <si>
     <t>osmo128w8qtnpchawwqraymhnvc0ygg6ecwure6heqt</t>
   </si>
   <si>
+    <t>1630000000</t>
+  </si>
+  <si>
     <t>osmo12gruedvrv0h9r0zz87z5jg70xly0rthr2zqclf</t>
   </si>
   <si>
+    <t>1023635676</t>
+  </si>
+  <si>
     <t>osmo122xq6xe80jk5zkhul6zzh80n2k69yr2e326qtl</t>
   </si>
   <si>
+    <t>osmo12v736nuytn9rjl5dpqtfxzdg40vtlwqqgrfahd</t>
+  </si>
+  <si>
+    <t>1024005229</t>
+  </si>
+  <si>
+    <t>osmo12dz0vh9gk50wsjc7jvefs7l8fafraalcctyhk4</t>
+  </si>
+  <si>
+    <t>1023961168</t>
+  </si>
+  <si>
+    <t>osmo12dmhexy2lm8rsdsl0yclyjpuep6q2w5p43eyau</t>
+  </si>
+  <si>
     <t>osmo12w932cswf7lp9q2lfmwz2nuhjy4uawqwuhjj6h</t>
   </si>
   <si>
+    <t>1350000000</t>
+  </si>
+  <si>
+    <t>osmo120s8u8s6v2we2qvddjjx2du74fe2ln8qasexy2</t>
+  </si>
+  <si>
+    <t>osmo12e6uk8wxal4af8ng9apfs97ytxyddremaw4gx5</t>
+  </si>
+  <si>
+    <t>5091000000</t>
+  </si>
+  <si>
     <t>osmo12el8k6fz3n80mv2czz6apdxplsnpxznagtsgc4</t>
   </si>
   <si>
+    <t>859590585</t>
+  </si>
+  <si>
     <t>osmo1trpqkzdzprkregdez3xs5mf9w3me76gyu83dnhc2fjxuy9g70unqs5v62q</t>
   </si>
   <si>
+    <t>10066530415</t>
+  </si>
+  <si>
     <t>osmo1tyu6854q0vlsqpmvaasr9043cwfrtmu4n76859</t>
   </si>
   <si>
+    <t>1001000000</t>
+  </si>
+  <si>
+    <t>osmo1tgyqvzknt3l0qv6p98guu859mv8htpz622zvws</t>
+  </si>
+  <si>
+    <t>1003000000</t>
+  </si>
+  <si>
     <t>osmo1t2vtt4qzhcgg04czu327vaxz0v5drg2wckdtg8</t>
   </si>
   <si>
+    <t>1001684368</t>
+  </si>
+  <si>
+    <t>osmo1ttyy7fz35e8m83ypdujvlhrr39h2eesy8xfjp8</t>
+  </si>
+  <si>
+    <t>1041859457</t>
+  </si>
+  <si>
+    <t>osmo1tscpg9f9gxfazg0eq4zztx4hgst5uz2u85ngk9</t>
+  </si>
+  <si>
     <t>osmo1th70a0kldrx9z7mchynthshr5rtxnru9eg2ds2</t>
   </si>
   <si>
+    <t>1089900000</t>
+  </si>
+  <si>
+    <t>osmo1t62c9n4ctdawhespk9042za7t73lwzxmzdawqk</t>
+  </si>
+  <si>
+    <t>osmo1tad96jc4608praayujdw957szd9krjg3r03d04</t>
+  </si>
+  <si>
+    <t>5083000000</t>
+  </si>
+  <si>
+    <t>osmo1vpjruh4nrczquguhqw9s4cc0pn69mw292lwcjh</t>
+  </si>
+  <si>
+    <t>1730101495</t>
+  </si>
+  <si>
+    <t>osmo1v8fwk5d36pr0zruc5p8fr872jauvgcupa6rqum</t>
+  </si>
+  <si>
+    <t>osmo1vvtwhcksz2ewm75ynfp2vxkaswp6q3zdrjdut6</t>
+  </si>
+  <si>
     <t>osmo1vkngvnelw4tgahyn20sr0kvk9jq8wrfe0hcalf</t>
   </si>
   <si>
+    <t>635758226</t>
+  </si>
+  <si>
     <t>osmo1dzz0hlf8uznvxwmgdd4su4euk8tmpys2cx2uw2</t>
   </si>
   <si>
+    <t>20343000000</t>
+  </si>
+  <si>
     <t>osmo1dxwkz5gd6ygfmthalupst7vkgcp0ehg2cwz8uy</t>
   </si>
   <si>
@@ -148,202 +427,397 @@
     <t>osmo1d3ds5wtlgjh800c9lka68puxpey3x2dehglqag</t>
   </si>
   <si>
+    <t>2126600000</t>
+  </si>
+  <si>
     <t>osmo1de88sp2h3955ktrjgnm0jkhy8dttsgdzagnxs0</t>
   </si>
   <si>
+    <t>4233759694</t>
+  </si>
+  <si>
     <t>osmo1duls39pg7uqze7vpz65n22re72nycvmr38246u</t>
   </si>
   <si>
+    <t>14416006965</t>
+  </si>
+  <si>
+    <t>osmo1wqjagmsh5tyv4eztpypqgklyq23aepxfg3kn4e</t>
+  </si>
+  <si>
+    <t>3096494037</t>
+  </si>
+  <si>
+    <t>osmo1wxv8jnx4tnr5rr5uwnx05g3s74tcpzajfpts3n</t>
+  </si>
+  <si>
+    <t>1142831365</t>
+  </si>
+  <si>
+    <t>osmo1wxhgzdwmek4duaevg2zwzguev8tnm4nctj4ast</t>
+  </si>
+  <si>
+    <t>700123981</t>
+  </si>
+  <si>
     <t>osmo1wgdegtthkx0n5fmyt2l2xn9jchywffac738e4z</t>
   </si>
   <si>
-    <t>osmo1wdnc6mfpcfs8md2cvm3gyfdzw8v3mcx8cmj6se</t>
+    <t>12077766287</t>
   </si>
   <si>
     <t>osmo1wjt0p3m62rrpugxug4szqgj4v5d3l8llfpns9a</t>
   </si>
   <si>
+    <t>1523629267</t>
+  </si>
+  <si>
     <t>osmo1wl3xq2ktgeu0xxyf27axqvnpufft6vjzfymk90</t>
   </si>
   <si>
+    <t>2054000000</t>
+  </si>
+  <si>
     <t>osmo10guvn4243qg2l8ey8gy9zwttz6v23232s7pv5u</t>
   </si>
   <si>
+    <t>32509000000</t>
+  </si>
+  <si>
     <t>osmo10u7mu6yygadq4ak27wqgsexhjx0dstjrc3m4ht</t>
   </si>
   <si>
+    <t>2042500000</t>
+  </si>
+  <si>
+    <t>osmo1sp32p0rr0rg89hjv40vksdwwquag60yffwnsz9</t>
+  </si>
+  <si>
+    <t>2000100000</t>
+  </si>
+  <si>
+    <t>osmo1sdf4z2y8rjekmtsgsy7zy56f4yhg33huuanmk4</t>
+  </si>
+  <si>
     <t>osmo1sj5zyq6pple07fsjfghy80wc0s38chrxnlr4e6</t>
   </si>
   <si>
+    <t>1005939921</t>
+  </si>
+  <si>
+    <t>osmo1sk9urdv9x8zttkz2r9ysfl3dnlapv0ugd9ftp8</t>
+  </si>
+  <si>
+    <t>osmo1shgmg4zeksmf4pkf06dlx4wt6vp44f0my9n527</t>
+  </si>
+  <si>
+    <t>osmo1s63zncrcargfau4xfmrpvzyn0hndg2n7m8rz8e</t>
+  </si>
+  <si>
+    <t>1442000000</t>
+  </si>
+  <si>
+    <t>osmo1sltq5xnhhh02zelpphpkqqfy48w7rg47k7d9rs</t>
+  </si>
+  <si>
+    <t>1555500000</t>
+  </si>
+  <si>
+    <t>osmo13zzlsjnauafxz764nvj6mgagrkt5vke3cflpxw</t>
+  </si>
+  <si>
+    <t>533993898</t>
+  </si>
+  <si>
+    <t>osmo13kx5ldwmphx6m00mxa3azdxu8rhmwe378r9nhw</t>
+  </si>
+  <si>
     <t>osmo13hapz35dfzuf9ult9vw7qdsag83r99qz9q7cw3</t>
   </si>
   <si>
+    <t>7804870234</t>
+  </si>
+  <si>
+    <t>osmo13atdnhurhy87dycp9t442wgqej79esvhmxrjqc</t>
+  </si>
+  <si>
     <t>osmo137tlv9g4dgm9jq9ucwcd5mpp7w4agtzutd62eq</t>
   </si>
   <si>
+    <t>10171828410</t>
+  </si>
+  <si>
     <t>osmo1jr0e4le4kr7ewtsvujrqzcyjqn9r026st528la</t>
   </si>
   <si>
-    <t>osmo1jtustv4ghy997d6catge3mgklszkvve66v5r7s</t>
-  </si>
-  <si>
-    <t>osmo1ja9uell4cj7a564fzdm7w7733um2mhnvkg0cx9</t>
-  </si>
-  <si>
-    <t>osmo1ngms94pfxec8qvpc84pn0kecwz9x3xjy0xe22u</t>
-  </si>
-  <si>
-    <t>osmo1n2wwtmmkgmsyfqyekkg5qakmrtf4s6xhqxpzy2</t>
-  </si>
-  <si>
-    <t>osmo1n3nk86e3xzv4flptpp8rvu6qrh5zrnr6g49ylt</t>
-  </si>
-  <si>
-    <t>osmo1nnh4thxglkdcp0h2kr7t53rqakrmlwvyq2jg5s</t>
-  </si>
-  <si>
-    <t>osmo1n5ycs4kv846zsku07xm29ltkyg2fs8xyhawncf</t>
-  </si>
-  <si>
-    <t>osmo1n5jj462cvekx8z0syz8u2gmpf46g2csx895h33</t>
-  </si>
-  <si>
-    <t>osmo1n6adng2ngpsyhxm37v9nr6c2elflunzkhtuwfv</t>
-  </si>
-  <si>
-    <t>osmo152l67q44deyj7t956f2swkjza5rznm2qpte2az</t>
-  </si>
-  <si>
-    <t>osmo15scds0jq9crvvphgmnkxuvnycj64xj9l9k4nwh</t>
-  </si>
-  <si>
-    <t>osmo14qc7f7nzae7kppwpxhymn54qwgx7tlcccde9f0</t>
-  </si>
-  <si>
-    <t>osmo14r9q9ntn0zncx7gtkzarcasgfmvwh86q92hxnx</t>
-  </si>
-  <si>
-    <t>osmo1480j70ftswdfnc5uf50u7r4ksd5qgd42jj9wg2</t>
-  </si>
-  <si>
-    <t>osmo145hnlzs7xge77qmahfjevac0lzzvkwulrssy8u</t>
-  </si>
-  <si>
-    <t>osmo14urmyd6fn962l0h6qnleqgzejf6zs3xsvpgcjv</t>
-  </si>
-  <si>
-    <t>osmo1kgu07r6lhpr0v3dww9a4rldfny5v6fyk43jnl3</t>
-  </si>
-  <si>
-    <t>osmo1kvq4n4n4x3gqlyfr672pjyqn73c2hdkulpslag</t>
-  </si>
-  <si>
-    <t>osmo1hv4rlv94dwwsj3z7l6muye6ndmup0hta7a4v3p</t>
-  </si>
-  <si>
-    <t>osmo1h3l6dyvhg0zsh403q6v5c9xpne8ucl8j399d7q</t>
-  </si>
-  <si>
-    <t>osmo1hkwgeez52gs20zx0sqwucs5qxauedf2a9fkwke</t>
-  </si>
-  <si>
-    <t>osmo1hu5ugwjnttk2nw63pfe5l9547gdatklk6m3nm4</t>
+    <t>2529894903</t>
+  </si>
+  <si>
+    <t>osmo1jttdtq9ah54rawwtsapt225unp8fdpedg0v4lc</t>
+  </si>
+  <si>
+    <t>659748911</t>
   </si>
   <si>
     <t>osmo1cqrky3t78np3a60kmdpylzyv594muagffwyf2x</t>
   </si>
   <si>
+    <t>1024273380</t>
+  </si>
+  <si>
+    <t>osmo1cxt9q4f43qhl7vnz73sqxnk65ux2lw9hc6k7aq</t>
+  </si>
+  <si>
     <t>osmo1c0k6p340st8egc7jcfndfm4jmly4na6ceq2f3u</t>
   </si>
   <si>
+    <t>1250000000</t>
+  </si>
+  <si>
+    <t>osmo1c4skq47cqsyteg8kfjf6v3ehhza000ph7p5yxt</t>
+  </si>
+  <si>
+    <t>3936368100</t>
+  </si>
+  <si>
     <t>osmo1cc9n326mgu9qkmg7fvmel7ax6ncg6vgsmvy8wf</t>
   </si>
   <si>
+    <t>541772971</t>
+  </si>
+  <si>
     <t>osmo1cclvds6qkapm7d6m8akag2z2kqgqct5gnzhd66</t>
   </si>
   <si>
+    <t>546600000</t>
+  </si>
+  <si>
     <t>osmo1c7r92jcmdqc7sxqtac97uapj5ptjggm96d6ge6</t>
   </si>
   <si>
+    <t>1088000000</t>
+  </si>
+  <si>
+    <t>osmo1era3cnmp4hahctgqyhlc6evsj63ueahw39aze8</t>
+  </si>
+  <si>
+    <t>2300000646</t>
+  </si>
+  <si>
     <t>osmo1ege3jn6j509d7985jdefxtn7mcvngjp8ez8s66</t>
   </si>
   <si>
+    <t>1631347951</t>
+  </si>
+  <si>
+    <t>osmo1e0awhdyuzszse5xdde3nrwpg2jzhwu4f8ptz8j</t>
+  </si>
+  <si>
+    <t>3193361786</t>
+  </si>
+  <si>
     <t>osmo1e3ukvtjmrqhmwje70dhmqnvvt3tjpkrkcp7smh</t>
   </si>
   <si>
+    <t>37622020936</t>
+  </si>
+  <si>
     <t>osmo1e5jmcepmgr6wsmp4n3tlhmdcny2pw49cvvqydf</t>
   </si>
   <si>
+    <t>3128361000</t>
+  </si>
+  <si>
+    <t>osmo1ec8gcke3uc8qavull6cm0wtf3dl08qdejjw8uj</t>
+  </si>
+  <si>
     <t>osmo1emqzfcz5hezpg3z6ueqkptadpyx5qfujqpn4g9</t>
   </si>
   <si>
+    <t>675599383</t>
+  </si>
+  <si>
     <t>osmo1eujlkkfsyjf28ey9vce3yp0s0mdd0l94y9s3le</t>
   </si>
   <si>
+    <t>10000000000</t>
+  </si>
+  <si>
     <t>osmo1e7hqwdqjtr428ynukkmfx524v24mgqznyqk7d8</t>
   </si>
   <si>
+    <t>1035000000</t>
+  </si>
+  <si>
+    <t>osmo1el8vjd3j7rwt5dr76hqkneez69csul50fehhgp</t>
+  </si>
+  <si>
+    <t>5071000000</t>
+  </si>
+  <si>
+    <t>osmo16yzm6qjjheafnyvlcjxnkmhj3hullgplp8grxc</t>
+  </si>
+  <si>
+    <t>1024085367</t>
+  </si>
+  <si>
+    <t>osmo169pkmuffdpwm8dfrefc2tcsvhyv74x8rq30gzx</t>
+  </si>
+  <si>
+    <t>541690180</t>
+  </si>
+  <si>
+    <t>osmo162um8tckdsm90a7r3dp044akk9twfhvgj996z9</t>
+  </si>
+  <si>
+    <t>osmo16tfjyefrgekf0l8zzccjy2c72nh2mscj2sgkxk</t>
+  </si>
+  <si>
+    <t>1023765257</t>
+  </si>
+  <si>
     <t>osmo165nqrnqep5e487wzgmydw7fjz6haq4v3x3x9ca</t>
   </si>
   <si>
+    <t>2058000000</t>
+  </si>
+  <si>
+    <t>osmo16ukp2nyns63r9kj3sucpxf3szqmteu03tpzetj</t>
+  </si>
+  <si>
+    <t>osmo1mfnw9skcj7crespne7fp30ljhy2cxhzva50qyq</t>
+  </si>
+  <si>
+    <t>5041000000</t>
+  </si>
+  <si>
     <t>osmo1m20wyugxnse56q2lfmm9txyk2fx39s6fx5sx8f</t>
   </si>
   <si>
+    <t>700000000</t>
+  </si>
+  <si>
     <t>osmo1mwmapvdzrc9hezq8r8lfmpzqu4zmsj2yjxq397</t>
   </si>
   <si>
+    <t>1121814317</t>
+  </si>
+  <si>
+    <t>osmo1mk4r7gngs4pw3vgnp4stllyfs22jnesl56d5ke</t>
+  </si>
+  <si>
     <t>osmo1mkk7xd9tll96rt2j8e8tamggu5agzwq7wyarp9</t>
   </si>
   <si>
+    <t>3700000032</t>
+  </si>
+  <si>
     <t>osmo1mud3fuxt5zw4kfysd9gjrn6fjj5rz9g6m9fx9k</t>
   </si>
   <si>
+    <t>18271000000</t>
+  </si>
+  <si>
     <t>osmo1mlngv32gknshsrny2f8cw52r552836se3qrcfk</t>
   </si>
   <si>
-    <t>osmo1u28uvarg9j5hxhhrsy8uuagvfe9qm5t3cv074k</t>
+    <t>1011419250</t>
+  </si>
+  <si>
+    <t>osmo1u96uszryc79d4vppl3sy2e9ha9h8cc7fsvh4cp</t>
   </si>
   <si>
     <t>osmo1u36qa4gluu2drp89jj0978c2g7d9j607ldv4vm</t>
   </si>
   <si>
+    <t>563140139</t>
+  </si>
+  <si>
+    <t>osmo1ujepumwuauf5dv4jjc686f6xj4u29rtpk5xrjs</t>
+  </si>
+  <si>
+    <t>638093742</t>
+  </si>
+  <si>
     <t>osmo1ukv0u57kpgjc8ft7hk842dr8gxryjftyh0w25w</t>
   </si>
   <si>
     <t>osmo1ayy0y3lex3wkhcp7y5y6s439nv3k78egrujyw0</t>
   </si>
   <si>
+    <t>1269200000</t>
+  </si>
+  <si>
     <t>osmo1a9u8yv5v0wu5atynlh33hm04l67y9e6x2px6gn</t>
   </si>
   <si>
+    <t>osmo1ag5cgyzgk2xzyrw3xkxk7rjz4lxwssgn7p6d7p</t>
+  </si>
+  <si>
     <t>osmo1a2l3cfqllu9qs6437mqkq59ygfx378p9sk480q</t>
   </si>
   <si>
+    <t>1041000000</t>
+  </si>
+  <si>
     <t>osmo1a3858f250ve4t6rp9ef2svpr7sj20aaxgy8dyu</t>
   </si>
   <si>
+    <t>637305404</t>
+  </si>
+  <si>
     <t>osmo17yf8hsgezzhtl58gp3sqe7dcsj2wpqtzexqrka</t>
   </si>
   <si>
+    <t>11111000000</t>
+  </si>
+  <si>
+    <t>osmo179qawzj2ncf9uknfjw6z3zxpvc33cylqemy678</t>
+  </si>
+  <si>
     <t>osmo178n4m7j5hlu5evjqpyg773zje2dra5rhzr74mz</t>
   </si>
   <si>
-    <t>osmo17t908frmwcuqd83nsx3ydsxx6gfy6dzlrsdygy</t>
+    <t>561019431</t>
   </si>
   <si>
     <t>osmo17dndad55zly50aj8lzzklxusevdz0r0gvzqkrc</t>
   </si>
   <si>
+    <t>2049000000</t>
+  </si>
+  <si>
     <t>osmo17hr0kwjgklazhufht4sdpllmvm6047wdupdds7</t>
   </si>
   <si>
+    <t>1482303449</t>
+  </si>
+  <si>
+    <t>osmo176csrl54fys3cd0gmhkpmwns2gtngfca8kssu9</t>
+  </si>
+  <si>
+    <t>osmo177n4ptnw3utwjlrk8n28t4zf00afm379qrkkks</t>
+  </si>
+  <si>
+    <t>3397902970</t>
+  </si>
+  <si>
+    <t>osmo1lxtwpxd3veex3f4w99zhj7f9u4jl75qaf6sd8m</t>
+  </si>
+  <si>
     <t>osmo1lx0my7kk7uy75y68r602ga62l7n8cwawqhglt6</t>
   </si>
   <si>
-    <t>osmo1lft50ldy04u3szywhg38cnfpxfg7r5487amng4</t>
+    <t>2780739026</t>
+  </si>
+  <si>
+    <t>osmo1l3dr30jzea6rac93eea34urypdgumref7sh2j6</t>
   </si>
   <si>
     <t>osmo1lul42lw2p4mv2mlte89cf4qnfg2jfduuy7lnuf</t>
+  </si>
+  <si>
+    <t>54902064764</t>
   </si>
 </sst>
 </file>
@@ -720,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -738,872 +1212,1208 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>3000000</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>2000000</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>1000000</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1000000</v>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1000000</v>
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>3000000</v>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>1000000</v>
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>1000000</v>
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>1000000</v>
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>1000000</v>
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>1000000</v>
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>1000000</v>
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>3000000</v>
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>1000000</v>
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>1000000</v>
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>5000000</v>
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>1000000</v>
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>1000000</v>
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>1000000</v>
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>2000000</v>
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>1000000</v>
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>1000000</v>
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>1000000</v>
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>2000000</v>
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>1000000</v>
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>1000000</v>
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>3000000</v>
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>1000000</v>
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>2000000</v>
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>1000000</v>
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>1000000</v>
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>2000000</v>
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>1000000</v>
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>1000000</v>
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>2000000</v>
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>1000000</v>
+        <v>69</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>1000000</v>
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>1000000</v>
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>1000000</v>
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>3000000</v>
+        <v>74</v>
+      </c>
+      <c r="B41" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>1000000</v>
+        <v>76</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>1000000</v>
+        <v>78</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>3000000</v>
+        <v>80</v>
+      </c>
+      <c r="B44" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>1000000</v>
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46">
-        <v>3000000</v>
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47">
-        <v>3000000</v>
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48">
-        <v>1000000</v>
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49">
-        <v>1000000</v>
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50">
-        <v>1000000</v>
+        <v>91</v>
+      </c>
+      <c r="B50" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51">
-        <v>5000000</v>
+        <v>93</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52">
-        <v>1000000</v>
+        <v>94</v>
+      </c>
+      <c r="B52" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53">
-        <v>1000000</v>
+        <v>96</v>
+      </c>
+      <c r="B53" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54">
-        <v>2000000</v>
+        <v>98</v>
+      </c>
+      <c r="B54" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55">
-        <v>3000000</v>
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56">
-        <v>1000000</v>
+        <v>101</v>
+      </c>
+      <c r="B56" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57">
-        <v>1000000</v>
+        <v>103</v>
+      </c>
+      <c r="B57" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58">
-        <v>1000000</v>
+        <v>104</v>
+      </c>
+      <c r="B58" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59">
-        <v>3000000</v>
+        <v>106</v>
+      </c>
+      <c r="B59" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60">
-        <v>1000000</v>
+        <v>107</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61">
-        <v>1000000</v>
+        <v>109</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62">
-        <v>1000000</v>
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63">
-        <v>1000000</v>
+        <v>113</v>
+      </c>
+      <c r="B63" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64">
-        <v>1000000</v>
+        <v>115</v>
+      </c>
+      <c r="B64" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65">
-        <v>1000000</v>
+        <v>117</v>
+      </c>
+      <c r="B65" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66">
-        <v>1000000</v>
+        <v>119</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67">
-        <v>1000000</v>
+        <v>121</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
-      </c>
-      <c r="B68">
-        <v>1000000</v>
+        <v>122</v>
+      </c>
+      <c r="B68" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69">
-        <v>1000000</v>
+        <v>124</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
-      </c>
-      <c r="B70">
-        <v>2000000</v>
+        <v>125</v>
+      </c>
+      <c r="B70" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
-      </c>
-      <c r="B71">
-        <v>1000000</v>
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72">
-        <v>1000000</v>
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73">
-        <v>3000000</v>
+        <v>130</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74">
-        <v>3000000</v>
+        <v>131</v>
+      </c>
+      <c r="B74" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
-      </c>
-      <c r="B75">
-        <v>1000000</v>
+        <v>133</v>
+      </c>
+      <c r="B75" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76">
-        <v>1000000</v>
+        <v>135</v>
+      </c>
+      <c r="B76" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77">
-        <v>2000000</v>
+        <v>136</v>
+      </c>
+      <c r="B77" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78">
-        <v>3000000</v>
+        <v>137</v>
+      </c>
+      <c r="B78" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79">
-        <v>1000000</v>
+        <v>139</v>
+      </c>
+      <c r="B79" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80">
-        <v>1000000</v>
+        <v>141</v>
+      </c>
+      <c r="B80" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81">
-        <v>1000000</v>
+        <v>143</v>
+      </c>
+      <c r="B81" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82">
-        <v>1000000</v>
+        <v>145</v>
+      </c>
+      <c r="B82" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83">
-        <v>1000000</v>
+        <v>147</v>
+      </c>
+      <c r="B83" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
-      </c>
-      <c r="B84">
-        <v>1000000</v>
+        <v>149</v>
+      </c>
+      <c r="B84" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
-      </c>
-      <c r="B85">
-        <v>5000000</v>
+        <v>151</v>
+      </c>
+      <c r="B85" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86">
-        <v>1000000</v>
+        <v>153</v>
+      </c>
+      <c r="B86" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
-      </c>
-      <c r="B87">
-        <v>1000000</v>
+        <v>155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88">
-        <v>1000000</v>
+        <v>157</v>
+      </c>
+      <c r="B88" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
-      </c>
-      <c r="B89">
-        <v>1000000</v>
+        <v>159</v>
+      </c>
+      <c r="B89" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
-      </c>
-      <c r="B90">
-        <v>1000000</v>
+        <v>161</v>
+      </c>
+      <c r="B90" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
-      </c>
-      <c r="B91">
-        <v>1000000</v>
+        <v>162</v>
+      </c>
+      <c r="B91" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
-      </c>
-      <c r="B92">
-        <v>1000000</v>
+        <v>164</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
-      </c>
-      <c r="B93">
-        <v>1000000</v>
+        <v>165</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94">
-        <v>3000000</v>
+        <v>166</v>
+      </c>
+      <c r="B94" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
-      </c>
-      <c r="B95">
-        <v>1000000</v>
+        <v>168</v>
+      </c>
+      <c r="B95" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
-      </c>
-      <c r="B96">
-        <v>5000000</v>
+        <v>170</v>
+      </c>
+      <c r="B96" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
-      </c>
-      <c r="B97">
-        <v>1000000</v>
+        <v>172</v>
+      </c>
+      <c r="B97" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
-      </c>
-      <c r="B98">
-        <v>3000000</v>
+        <v>173</v>
+      </c>
+      <c r="B98" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99">
-        <v>1000000</v>
+        <v>175</v>
+      </c>
+      <c r="B99" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
-      </c>
-      <c r="B100">
-        <v>1000000</v>
+        <v>176</v>
+      </c>
+      <c r="B100" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
-      </c>
-      <c r="B101">
-        <v>1000000</v>
+        <v>178</v>
+      </c>
+      <c r="B101" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>102</v>
-      </c>
-      <c r="B102">
-        <v>1000000</v>
+        <v>180</v>
+      </c>
+      <c r="B102" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>103</v>
-      </c>
-      <c r="B103">
-        <v>3000000</v>
+        <v>182</v>
+      </c>
+      <c r="B103" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>104</v>
-      </c>
-      <c r="B104">
-        <v>1000000</v>
+        <v>184</v>
+      </c>
+      <c r="B104" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>105</v>
-      </c>
-      <c r="B105">
-        <v>3000000</v>
+        <v>185</v>
+      </c>
+      <c r="B105" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>106</v>
-      </c>
-      <c r="B106">
-        <v>1000000</v>
+        <v>187</v>
+      </c>
+      <c r="B106" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>107</v>
-      </c>
-      <c r="B107">
-        <v>1000000</v>
+        <v>189</v>
+      </c>
+      <c r="B107" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>108</v>
-      </c>
-      <c r="B108">
-        <v>1000000</v>
+        <v>191</v>
+      </c>
+      <c r="B108" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>109</v>
-      </c>
-      <c r="B109">
-        <v>1000000</v>
+        <v>193</v>
+      </c>
+      <c r="B109" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>110</v>
-      </c>
-      <c r="B110">
-        <v>5000000</v>
+        <v>195</v>
+      </c>
+      <c r="B110" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>197</v>
+      </c>
+      <c r="B111" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>199</v>
+      </c>
+      <c r="B112" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>201</v>
+      </c>
+      <c r="B113" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>203</v>
+      </c>
+      <c r="B114" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>205</v>
+      </c>
+      <c r="B115" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>206</v>
+      </c>
+      <c r="B116" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>208</v>
+      </c>
+      <c r="B117" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>210</v>
+      </c>
+      <c r="B118" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>212</v>
+      </c>
+      <c r="B119" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>214</v>
+      </c>
+      <c r="B120" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>216</v>
+      </c>
+      <c r="B121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>218</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>219</v>
+      </c>
+      <c r="B123" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>221</v>
+      </c>
+      <c r="B124" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>223</v>
+      </c>
+      <c r="B125" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>224</v>
+      </c>
+      <c r="B126" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>226</v>
+      </c>
+      <c r="B127" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>228</v>
+      </c>
+      <c r="B128" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>230</v>
+      </c>
+      <c r="B129" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>231</v>
+      </c>
+      <c r="B130" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>233</v>
+      </c>
+      <c r="B131" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>235</v>
+      </c>
+      <c r="B132" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>237</v>
+      </c>
+      <c r="B133" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>238</v>
+      </c>
+      <c r="B134" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>240</v>
+      </c>
+      <c r="B135" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>242</v>
+      </c>
+      <c r="B136" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>243</v>
+      </c>
+      <c r="B137" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>245</v>
+      </c>
+      <c r="B138" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>246</v>
+      </c>
+      <c r="B139" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>247</v>
+      </c>
+      <c r="B140" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>249</v>
+      </c>
+      <c r="B141" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>251</v>
+      </c>
+      <c r="B142" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>253</v>
+      </c>
+      <c r="B143" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>254</v>
+      </c>
+      <c r="B144" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>256</v>
+      </c>
+      <c r="B145" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>258</v>
+      </c>
+      <c r="B146" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>260</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>261</v>
+      </c>
+      <c r="B148" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>263</v>
+      </c>
+      <c r="B149" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>264</v>
+      </c>
+      <c r="B150" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>266</v>
+      </c>
+      <c r="B151" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>267</v>
+      </c>
+      <c r="B152" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
